--- a/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
@@ -82,10 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -97,13 +100,13 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>VALLEJO</t>
@@ -115,13 +118,13 @@
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -131,9 +134,6 @@
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
   </si>
 </sst>
 </file>
@@ -703,16 +703,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>61.9</v>
+      </c>
+      <c r="H2">
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -726,16 +729,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -749,16 +755,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -772,16 +781,19 @@
         <v>18</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>72.22</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -795,16 +807,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>82.61</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -860,16 +875,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -886,16 +901,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -921,7 +936,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -938,16 +953,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>72.22</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -964,16 +979,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>73.91</v>
+        <v>82.61</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1015,7 +1030,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920199</v>
+        <v>23330051920324</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1038,7 +1053,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920393</v>
+        <v>22330051920196</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1050,10 +1065,10 @@
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,7 +1076,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920394</v>
+        <v>22330051920205</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1079,12 +1094,12 @@
         <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920374</v>
+        <v>22330051920394</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1107,7 +1122,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920222</v>
+        <v>22330051920374</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1130,7 +1145,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920229</v>
+        <v>22330051920222</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>

--- a/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,33 +82,36 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>LIBRADO</t>
   </si>
   <si>
     <t>CRISTOBAL</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>VALLEJO</t>
   </si>
   <si>
@@ -118,13 +121,16 @@
     <t>PALACIOS</t>
   </si>
   <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
     <t>ARMANDO GABRIEL</t>
   </si>
   <si>
     <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -998,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1030,7 +1036,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920324</v>
+        <v>23330051920191</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1039,13 +1045,13 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1053,7 +1059,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920196</v>
+        <v>22330051920205</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1062,13 +1068,13 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1076,7 +1082,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920205</v>
+        <v>23330051920324</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1085,21 +1091,21 @@
         <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920394</v>
+        <v>22330051920196</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1108,13 +1114,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1122,16 +1128,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920374</v>
+        <v>22330051920394</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1145,16 +1151,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920222</v>
+        <v>22330051920374</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1163,6 +1169,29 @@
         <v>14</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920222</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="66">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,33 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -100,6 +127,27 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
     <t>VALIENTE</t>
   </si>
   <si>
@@ -119,6 +167,33 @@
   </si>
   <si>
     <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
   </si>
   <si>
     <t>DIEGO DE JESUS</t>
@@ -1004,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1036,62 +1111,62 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920191</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920205</v>
+        <v>23330051920189</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920324</v>
+        <v>23330051920202</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1100,98 +1175,305 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920196</v>
+        <v>21330051920396</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920394</v>
+        <v>22330051920405</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920374</v>
+        <v>22330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
+        <v>21330051920133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920271</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920395</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920191</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920324</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920394</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920374</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
         <v>22330051920222</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
         <v>14</v>
       </c>
-      <c r="G8">
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
@@ -91,36 +91,36 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -136,30 +136,30 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>GALINDO</t>
   </si>
   <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
     <t>VALLEJO</t>
   </si>
   <si>
@@ -178,34 +178,34 @@
     <t>LAZARO</t>
   </si>
   <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
     <t>BRANDON</t>
   </si>
   <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
     <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>ARMANDO GABRIEL</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -716,7 +716,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -725,13 +725,13 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +885,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -894,13 +894,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1063,10 +1063,10 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -1180,59 +1180,59 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>23330051920271</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
         <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920405</v>
+        <v>23330051920191</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920279</v>
+        <v>22330051920405</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>55</v>
@@ -1244,18 +1244,18 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920133</v>
+        <v>22330051920279</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1267,35 +1267,35 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920271</v>
+        <v>21330051920133</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920395</v>
+        <v>23330051920324</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1307,18 +1307,18 @@
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920191</v>
+        <v>22330051920196</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1333,15 +1333,15 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920205</v>
+        <v>21330051920396</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1356,15 +1356,15 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920324</v>
+        <v>22330051920395</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1376,10 +1376,10 @@
         <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920196</v>
+        <v>22330051920205</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -1399,10 +1399,10 @@
         <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         <v>22330051920394</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>

--- a/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -82,61 +82,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
   </si>
   <si>
     <t>JOSE</t>
@@ -145,18 +133,6 @@
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -169,40 +145,25 @@
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
   </si>
   <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO GABRIEL</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
   </si>
   <si>
     <t>EMILIANO GERARDO</t>
@@ -956,16 +917,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>61.9</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -982,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1017,7 +978,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1079,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1111,16 +1072,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920183</v>
+        <v>22330051920050</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1129,113 +1090,113 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920189</v>
+        <v>23330051920256</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920202</v>
+        <v>21330051920396</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920271</v>
+        <v>22330051920405</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920191</v>
+        <v>22330051920395</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920405</v>
+        <v>22330051920279</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1244,21 +1205,21 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920279</v>
+        <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1267,50 +1228,50 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920133</v>
+        <v>22330051920205</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920324</v>
+        <v>22330051920394</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1318,22 +1279,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920196</v>
+        <v>22330051920374</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1341,139 +1302,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920396</v>
+        <v>22330051920222</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920395</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920205</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920394</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920374</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920222</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -88,94 +88,16 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>CANDELARIO</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
     <t>ANGEL CHARBEL</t>
   </si>
   <si>
     <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
   </si>
 </sst>
 </file>
@@ -995,16 +917,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>72.22</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1021,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1078,10 +1000,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1101,10 +1023,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1113,213 +1035,6 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920396</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920405</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920395</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920279</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920205</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920394</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920374</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920222</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>
